--- a/tools/importer/reports/import-leg-vein-disease-symptom-checker.report.xlsx
+++ b/tools/importer/reports/import-leg-vein-disease-symptom-checker.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,31 @@
     <t>leg-vein-disease-symptom-checker</t>
   </si>
   <si>
-    <t>2026-09-15T10:18:47.035Z</t>
+    <t>2026-09-15T11:06:12.943Z</t>
   </si>
   <si>
     <t>Medtronic Vein Disease Symptom Checker</t>
   </si>
   <si>
     <t>https://www.medtronic.com/content/dam/medtronic-wide/public/united-states/products/cardiac-vascular/cardiovascular/superficial-vein/symptom-checker-leg-vein-disease/leg-vein-disease-symptom-checker/index.html</t>
+  </si>
+  <si>
+    <t>content/dam/medtronic-wide/public/united-states/products/cardiac-vascular/cardiovascular/superficial-vein/symptom-checker-leg-vein-disease/leg-vein-disease-symptom-checker/quiz.report.json</t>
+  </si>
+  <si>
+    <t>["quiz"]</t>
+  </si>
+  <si>
+    <t>content/dam/medtronic-wide/public/united-states/products/cardiac-vascular/cardiovascular/superficial-vein/symptom-checker-leg-vein-disease/leg-vein-disease-symptom-checker/quiz</t>
+  </si>
+  <si>
+    <t>leg-vein-disease-symptom-checker-quiz</t>
+  </si>
+  <si>
+    <t>2026-09-15T10:59:35.253Z</t>
+  </si>
+  <si>
+    <t>https://www.medtronic.com/content/dam/medtronic-wide/public/united-states/products/cardiac-vascular/cardiovascular/superficial-vein/symptom-checker-leg-vein-disease/leg-vein-disease-symptom-checker/quiz.html</t>
   </si>
 </sst>
 </file>
@@ -447,13 +465,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="5" max="5" width="39" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
@@ -511,6 +529,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
